--- a/output/pdf_financials_xlsx/VLD.xlsx
+++ b/output/pdf_financials_xlsx/VLD.xlsx
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.920936</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.294896</v>
       </c>
     </row>
     <row r="119">
@@ -3100,7 +3100,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>-0.920936</v>
       </c>

--- a/output/pdf_financials_xlsx/VLD.xlsx
+++ b/output/pdf_financials_xlsx/VLD.xlsx
@@ -579,10 +579,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.056145</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.041272</v>
       </c>
     </row>
     <row r="13">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.271092</v>
+        <v>-0.327237</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.546987</v>
+        <v>-0.588259</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.271092</v>
+        <v>-0.327237</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.546987</v>
+        <v>-0.588259</v>
       </c>
     </row>
     <row r="30">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">

--- a/output/pdf_financials_xlsx/VLD.xlsx
+++ b/output/pdf_financials_xlsx/VLD.xlsx
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.030655</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.030655</v>
       </c>
     </row>
     <row r="29">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.327237</v>
+        <v>-0.296582</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.588259</v>
+        <v>-0.557604</v>
       </c>
     </row>
     <row r="30">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.030655</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.030655</v>
       </c>
     </row>
     <row r="101">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>1.050637</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2892,7 +2892,11 @@
           <t>Depreciation and amortization expense</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.030655</v>
       </c>
@@ -3206,7 +3210,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>1.050637</v>
       </c>
@@ -3568,7 +3576,11 @@
           <t>Depreciation and amortization expense (note 5)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.030655</v>
       </c>
